--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8411-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8411-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9650FBD1-3E59-45A6-A1BB-16E3EDADB5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DA88951-B8F4-4488-8473-B68CA93975AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{9FB2BE48-60CB-4F37-8DDC-BCC0EEB05CE2}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3C6E4E5E-FB74-4893-91E6-1904085459BA}"/>
   </bookViews>
   <sheets>
     <sheet name="8411-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1511,25 +1511,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5F05EB-757E-4CA3-9D6B-13F9299CC14E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B46411-B5F3-4FA7-A347-E4ACD3195B49}">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1587,7 +1587,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1683,7 +1683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2025</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2024</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2023</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>25</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>25</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2022</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>25</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>25</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2021</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>25</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>25</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>25</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>25</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2020</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>25</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>25</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>25</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>25</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2019</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2018</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2017</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2016</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2015</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2014</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>2013</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>2012</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>2011</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>2010</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
         <v>56</v>
       </c>
